--- a/en/downloads/data-excel/7.3.1.2.xlsx
+++ b/en/downloads/data-excel/7.3.1.2.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB62504-A58A-4643-970D-7D45BE7BC779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -265,11 +266,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -286,6 +287,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="Times New Roman Cyr"/>
       <family val="1"/>
@@ -400,16 +409,48 @@
       <name val="Arial Cyr"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="6.15"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="4.5"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial Cyr"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="63"/>
+        <bgColor indexed="62"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="63"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -437,104 +478,169 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color indexed="59"/>
+      </left>
+      <right style="hair">
+        <color indexed="59"/>
+      </right>
+      <top style="hair">
+        <color indexed="59"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="59"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="8">
+  <cellStyleXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="3" fontId="22" fillId="2" borderId="3">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="3" borderId="4">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" applyNumberFormat="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="4" applyNumberFormat="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="3" applyFill="0" applyProtection="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="4" applyFill="0" applyProtection="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="8">
-    <cellStyle name="Normal 17" xfId="3"/>
-    <cellStyle name="Normal 2" xfId="5"/>
-    <cellStyle name="Normal_GDP1" xfId="7"/>
+  <cellStyles count="21">
+    <cellStyle name="Normal 17" xfId="3" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Normal 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2 2" xfId="8" xr:uid="{27CCCCA9-1A1C-4109-985A-C944F8A899D7}"/>
+    <cellStyle name="Normal_ADO_TEMPLATE1f" xfId="9" xr:uid="{D3DC5A5F-79A7-49E7-954C-EBC87B465419}"/>
+    <cellStyle name="Normal_GDP1" xfId="7" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="s80" xfId="10" xr:uid="{F32A017E-9EC5-46C5-AE2B-FCA296CDAAD3}"/>
+    <cellStyle name="s80 2" xfId="11" xr:uid="{DB80FC5D-CDB7-4057-B8BC-2BA8F9702FBB}"/>
+    <cellStyle name="s85" xfId="12" xr:uid="{59B447C9-486F-44FE-B7A8-90604E904810}"/>
+    <cellStyle name="s85 2" xfId="13" xr:uid="{1E555739-C796-46E6-A291-A554136317AC}"/>
+    <cellStyle name="s94" xfId="14" xr:uid="{363A92FC-F01A-4096-956C-A171776240E8}"/>
+    <cellStyle name="s94 2" xfId="15" xr:uid="{6EC7C3EA-E076-4A1C-9DF6-AB7B2A1FD5D6}"/>
+    <cellStyle name="s95" xfId="16" xr:uid="{DA29394B-1499-4B76-B339-D2EB3E77847A}"/>
+    <cellStyle name="s95 2" xfId="17" xr:uid="{EE648370-2915-4DD0-B0FC-2276663FD063}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 4" xfId="6"/>
-    <cellStyle name="Обычный 6" xfId="2"/>
-    <cellStyle name="Обычный 7" xfId="4"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Обычный 3" xfId="18" xr:uid="{CA812D18-4424-4C9D-B412-5F13C16355D9}"/>
+    <cellStyle name="Обычный 4" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Обычный 6" xfId="2" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Обычный 6 2" xfId="20" xr:uid="{F084DB1D-4157-4F59-B8EF-082BF7EF2577}"/>
+    <cellStyle name="Обычный 6 3" xfId="19" xr:uid="{F9277BE0-0362-4F2A-A2BE-05A3B43FD987}"/>
+    <cellStyle name="Обычный 7" xfId="4" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -550,9 +656,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -590,9 +696,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -627,7 +733,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -662,7 +768,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -835,48 +941,49 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="36.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="21.75" customHeight="1">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:20">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:20" s="24" customFormat="1" ht="12.75" thickBot="1">
-      <c r="A3" s="23"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
+    <row r="3" spans="1:21" s="17" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="18"/>
+      <c r="S3" s="18"/>
+      <c r="T3" s="18"/>
+      <c r="U3" s="22"/>
     </row>
-    <row r="4" spans="1:20" ht="15.75" thickBot="1">
+    <row r="4" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -886,350 +993,339 @@
       <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="10">
         <v>2007</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="10">
         <v>2008</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="10">
         <v>2009</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="10">
         <v>2010</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="10">
         <v>2011</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="10">
         <v>2012</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="10">
         <v>2013</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="10">
         <v>2014</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="10">
         <v>2015</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="10">
         <v>2016</v>
       </c>
-      <c r="N4" s="14">
+      <c r="N4" s="10">
         <v>2017</v>
       </c>
-      <c r="O4" s="16">
+      <c r="O4" s="11">
         <v>2018</v>
       </c>
-      <c r="P4" s="16">
+      <c r="P4" s="11">
         <v>2019</v>
       </c>
-      <c r="Q4" s="16">
+      <c r="Q4" s="11">
         <v>2020</v>
       </c>
-      <c r="R4" s="16">
+      <c r="R4" s="11">
         <v>2021</v>
       </c>
-      <c r="S4" s="16">
+      <c r="S4" s="11">
         <v>2022</v>
       </c>
-      <c r="T4" s="16">
+      <c r="T4" s="11">
         <v>2023</v>
       </c>
+      <c r="U4" s="23">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" ht="21.75" customHeight="1">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:21" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="14">
         <v>87.7</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="14">
         <v>59.8</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="14">
         <v>49.9</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="14">
         <v>47.7</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="14">
         <v>43.3</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="14">
         <v>43.7</v>
       </c>
-      <c r="J5" s="20">
+      <c r="J5" s="14">
         <v>38.5</v>
       </c>
-      <c r="K5" s="20">
+      <c r="K5" s="14">
         <v>36.9</v>
       </c>
-      <c r="L5" s="20">
+      <c r="L5" s="14">
         <v>31.5</v>
       </c>
-      <c r="M5" s="20">
+      <c r="M5" s="14">
         <v>27.9</v>
       </c>
-      <c r="N5" s="20">
+      <c r="N5" s="14">
         <v>26.9</v>
       </c>
-      <c r="O5" s="20">
+      <c r="O5" s="14">
         <v>26.3</v>
       </c>
-      <c r="P5" s="20">
+      <c r="P5" s="14">
         <v>23.111083656771282</v>
       </c>
-      <c r="Q5" s="20">
+      <c r="Q5" s="14">
         <v>24.08077930418019</v>
       </c>
-      <c r="R5" s="20">
+      <c r="R5" s="14">
         <v>19.336931533747723</v>
       </c>
-      <c r="S5" s="20">
+      <c r="S5" s="14">
         <v>13.600365850576139</v>
       </c>
-      <c r="T5" s="20">
+      <c r="T5" s="14">
         <v>10.376388024562692</v>
       </c>
+      <c r="U5" s="24">
+        <v>9.3101948089445496</v>
+      </c>
     </row>
-    <row r="6" spans="1:20" ht="39.75" customHeight="1">
+    <row r="6" spans="1:21" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="14">
         <v>20.5</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="14">
         <v>15</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="14">
         <v>15.6</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="14">
         <v>14.3</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="14">
         <v>14.3</v>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="14">
         <v>14.7</v>
       </c>
-      <c r="J6" s="20">
+      <c r="J6" s="14">
         <v>14.9</v>
       </c>
-      <c r="K6" s="20">
+      <c r="K6" s="14">
         <v>12.9</v>
       </c>
-      <c r="L6" s="20">
+      <c r="L6" s="14">
         <v>16.100000000000001</v>
       </c>
-      <c r="M6" s="20">
+      <c r="M6" s="14">
         <v>15.8</v>
       </c>
-      <c r="N6" s="20">
+      <c r="N6" s="14">
         <v>16.3</v>
       </c>
-      <c r="O6" s="20">
+      <c r="O6" s="14">
         <v>15.8</v>
       </c>
-      <c r="P6" s="20">
+      <c r="P6" s="14">
         <v>14.322631450320875</v>
       </c>
-      <c r="Q6" s="20">
+      <c r="Q6" s="14">
         <v>13.073459110725862</v>
       </c>
-      <c r="R6" s="20">
+      <c r="R6" s="14">
         <v>10.464141365743002</v>
       </c>
-      <c r="S6" s="20">
+      <c r="S6" s="14">
         <v>9.2742414863791556</v>
       </c>
-      <c r="T6" s="20">
+      <c r="T6" s="14">
         <v>9.6060616848577247</v>
       </c>
+      <c r="U6" s="24">
+        <v>10.286100846685907</v>
+      </c>
     </row>
-    <row r="7" spans="1:20" ht="27" customHeight="1">
+    <row r="7" spans="1:21" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="14">
         <v>71.8</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="14">
         <v>46</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="14">
         <v>40.1</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="14">
         <v>33.1</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="14">
         <v>30</v>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="14">
         <v>41.2</v>
       </c>
-      <c r="J7" s="20">
+      <c r="J7" s="14">
         <v>35</v>
       </c>
-      <c r="K7" s="20">
+      <c r="K7" s="14">
         <v>43</v>
       </c>
-      <c r="L7" s="20">
+      <c r="L7" s="14">
         <v>31.8</v>
       </c>
-      <c r="M7" s="20">
+      <c r="M7" s="14">
         <v>26.3</v>
       </c>
-      <c r="N7" s="20">
+      <c r="N7" s="14">
         <v>25</v>
       </c>
-      <c r="O7" s="20">
+      <c r="O7" s="14">
         <v>25.5</v>
       </c>
-      <c r="P7" s="20">
+      <c r="P7" s="14">
         <v>23.612622725489956</v>
       </c>
-      <c r="Q7" s="20">
+      <c r="Q7" s="14">
         <v>21.941290626870046</v>
       </c>
-      <c r="R7" s="20">
+      <c r="R7" s="14">
         <v>21.69437772849707</v>
       </c>
-      <c r="S7" s="20">
+      <c r="S7" s="14">
         <v>17.303523954725925</v>
       </c>
-      <c r="T7" s="20">
+      <c r="T7" s="14">
         <v>17.548015954891792</v>
       </c>
+      <c r="U7" s="24">
+        <v>14.184356547278464</v>
+      </c>
     </row>
-    <row r="8" spans="1:20" ht="30.75" customHeight="1" thickBot="1">
+    <row r="8" spans="1:21" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="15">
         <v>158.9</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="15">
         <v>146.9</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="15">
         <v>168.8</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="15">
         <v>180.5</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="15">
         <v>174.7</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="15">
         <v>155.19999999999999</v>
       </c>
-      <c r="J8" s="21">
+      <c r="J8" s="15">
         <v>160.30000000000001</v>
       </c>
-      <c r="K8" s="21">
+      <c r="K8" s="15">
         <v>130.9</v>
       </c>
-      <c r="L8" s="21">
+      <c r="L8" s="15">
         <v>207.6</v>
       </c>
-      <c r="M8" s="21">
+      <c r="M8" s="15">
         <v>248.3</v>
       </c>
-      <c r="N8" s="21">
+      <c r="N8" s="15">
         <v>260.3</v>
       </c>
-      <c r="O8" s="21">
+      <c r="O8" s="15">
         <v>202.9</v>
       </c>
-      <c r="P8" s="21">
+      <c r="P8" s="15">
         <v>200.5</v>
       </c>
-      <c r="Q8" s="21">
+      <c r="Q8" s="15">
         <v>196.6</v>
       </c>
-      <c r="R8" s="22">
+      <c r="R8" s="15">
         <v>206.4</v>
       </c>
-      <c r="S8" s="22">
+      <c r="S8" s="15">
         <v>205.5</v>
       </c>
-      <c r="T8" s="22">
+      <c r="T8" s="15">
         <v>196.7</v>
       </c>
+      <c r="U8" s="22"/>
     </row>
-    <row r="9" spans="1:20" ht="36" customHeight="1">
-      <c r="A9" s="27" t="s">
+    <row r="9" spans="1:21" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="15"/>
-      <c r="O9" s="15"/>
-      <c r="P9" s="15"/>
     </row>
-    <row r="10" spans="1:20">
-      <c r="B10" s="17"/>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B10" s="12"/>
     </row>
-    <row r="11" spans="1:20">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
